--- a/artfynd/A 16147-2022 artfynd.xlsx
+++ b/artfynd/A 16147-2022 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>132082483</v>
       </c>
       <c r="B3" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>132080892</v>
       </c>
       <c r="B5" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>132082444</v>
       </c>
       <c r="B6" t="n">
-        <v>83161</v>
+        <v>83163</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>132081105</v>
       </c>
       <c r="B7" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>132081052</v>
       </c>
       <c r="B8" t="n">
-        <v>92188</v>
+        <v>92191</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>132081586</v>
       </c>
       <c r="B9" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>132081046</v>
       </c>
       <c r="B10" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>132432303</v>
       </c>
       <c r="B11" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>132432289</v>
       </c>
       <c r="B12" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>132432277</v>
       </c>
       <c r="B13" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>132432280</v>
       </c>
       <c r="B14" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>132432279</v>
       </c>
       <c r="B15" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>132432294</v>
       </c>
       <c r="B16" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2224,10 +2224,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132432274</v>
+        <v>132432286</v>
       </c>
       <c r="B17" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,13 +2259,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596061</v>
+        <v>596083</v>
       </c>
       <c r="R17" t="n">
-        <v>6967031</v>
+        <v>6966954</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2331,10 +2331,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132432286</v>
+        <v>132432274</v>
       </c>
       <c r="B18" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596083</v>
+        <v>596061</v>
       </c>
       <c r="R18" t="n">
-        <v>6966954</v>
+        <v>6967031</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2438,10 +2438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132432297</v>
+        <v>132432301</v>
       </c>
       <c r="B19" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2473,13 +2473,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596078</v>
+        <v>596009</v>
       </c>
       <c r="R19" t="n">
-        <v>6966887</v>
+        <v>6966905</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2548,7 +2548,7 @@
         <v>132432283</v>
       </c>
       <c r="B20" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2652,10 +2652,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132432301</v>
+        <v>132432297</v>
       </c>
       <c r="B21" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2687,13 +2687,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596009</v>
+        <v>596078</v>
       </c>
       <c r="R21" t="n">
-        <v>6966905</v>
+        <v>6966887</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2762,7 +2762,7 @@
         <v>132432306</v>
       </c>
       <c r="B22" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>132432282</v>
       </c>
       <c r="B23" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>132432299</v>
       </c>
       <c r="B24" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>132432288</v>
       </c>
       <c r="B25" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>132432305</v>
       </c>
       <c r="B27" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>132432293</v>
       </c>
       <c r="B28" t="n">
-        <v>97960</v>
+        <v>97963</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>132432302</v>
       </c>
       <c r="B29" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3628,10 +3628,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132432281</v>
+        <v>132432275</v>
       </c>
       <c r="B30" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3663,13 +3663,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>596063</v>
+        <v>596090</v>
       </c>
       <c r="R30" t="n">
-        <v>6966956</v>
+        <v>6967008</v>
       </c>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3735,10 +3735,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132432275</v>
+        <v>132432281</v>
       </c>
       <c r="B31" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3770,13 +3770,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>596090</v>
+        <v>596063</v>
       </c>
       <c r="R31" t="n">
-        <v>6967008</v>
+        <v>6966956</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3845,7 +3845,7 @@
         <v>132432290</v>
       </c>
       <c r="B32" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>132432291</v>
       </c>
       <c r="B33" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>132432295</v>
       </c>
       <c r="B34" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>132432296</v>
       </c>
       <c r="B35" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4275,32 +4275,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132432304</v>
+        <v>132432300</v>
       </c>
       <c r="B36" t="n">
-        <v>79315</v>
+        <v>93180</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4310,13 +4310,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>596049</v>
+        <v>596083</v>
       </c>
       <c r="R36" t="n">
-        <v>6966812</v>
+        <v>6966915</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4382,32 +4382,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132432285</v>
+        <v>132432304</v>
       </c>
       <c r="B37" t="n">
-        <v>99095</v>
+        <v>79317</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4417,13 +4417,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>596048</v>
+        <v>596049</v>
       </c>
       <c r="R37" t="n">
-        <v>6967002</v>
+        <v>6966812</v>
       </c>
       <c r="S37" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4462,12 +4462,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:22</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>21 ex</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4494,32 +4489,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132432300</v>
+        <v>132432285</v>
       </c>
       <c r="B38" t="n">
-        <v>93177</v>
+        <v>99098</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4529,10 +4524,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>596083</v>
+        <v>596048</v>
       </c>
       <c r="R38" t="n">
-        <v>6966915</v>
+        <v>6967002</v>
       </c>
       <c r="S38" t="n">
         <v>7</v>
@@ -4564,7 +4559,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4574,7 +4569,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>21 ex</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4601,10 +4601,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132432307</v>
+        <v>132432287</v>
       </c>
       <c r="B39" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4612,45 +4612,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Remmen, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>596056</v>
+        <v>596092</v>
       </c>
       <c r="R39" t="n">
-        <v>6966834</v>
+        <v>6966931</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4679,7 +4671,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4689,12 +4681,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:33</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4721,10 +4708,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132432287</v>
+        <v>132432307</v>
       </c>
       <c r="B40" t="n">
-        <v>79315</v>
+        <v>57948</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4732,37 +4719,45 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Remmen, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>596092</v>
+        <v>596056</v>
       </c>
       <c r="R40" t="n">
-        <v>6966931</v>
+        <v>6966834</v>
       </c>
       <c r="S40" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4791,7 +4786,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4801,7 +4796,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4831,7 +4831,7 @@
         <v>132432298</v>
       </c>
       <c r="B41" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>132432292</v>
       </c>
       <c r="B42" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 16147-2022 artfynd.xlsx
+++ b/artfynd/A 16147-2022 artfynd.xlsx
@@ -3842,7 +3842,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132432290</v>
+        <v>132432291</v>
       </c>
       <c r="B32" t="n">
         <v>79317</v>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>596147</v>
+        <v>596166</v>
       </c>
       <c r="R32" t="n">
-        <v>6966886</v>
+        <v>6966844</v>
       </c>
       <c r="S32" t="n">
         <v>6</v>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3949,7 +3949,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132432291</v>
+        <v>132432290</v>
       </c>
       <c r="B33" t="n">
         <v>79317</v>
@@ -3984,10 +3984,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>596166</v>
+        <v>596147</v>
       </c>
       <c r="R33" t="n">
-        <v>6966844</v>
+        <v>6966886</v>
       </c>
       <c r="S33" t="n">
         <v>6</v>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4275,32 +4275,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132432300</v>
+        <v>132432285</v>
       </c>
       <c r="B36" t="n">
-        <v>93180</v>
+        <v>99098</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>596083</v>
+        <v>596048</v>
       </c>
       <c r="R36" t="n">
-        <v>6966915</v>
+        <v>6967002</v>
       </c>
       <c r="S36" t="n">
         <v>7</v>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4355,7 +4355,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>21 ex</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4382,32 +4387,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132432304</v>
+        <v>132432300</v>
       </c>
       <c r="B37" t="n">
-        <v>79317</v>
+        <v>93180</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4417,13 +4422,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>596049</v>
+        <v>596083</v>
       </c>
       <c r="R37" t="n">
-        <v>6966812</v>
+        <v>6966915</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4452,7 +4457,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4462,7 +4467,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4489,32 +4494,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132432285</v>
+        <v>132432304</v>
       </c>
       <c r="B38" t="n">
-        <v>99098</v>
+        <v>79317</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4524,13 +4529,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>596048</v>
+        <v>596049</v>
       </c>
       <c r="R38" t="n">
-        <v>6967002</v>
+        <v>6966812</v>
       </c>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4559,7 +4564,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4569,12 +4574,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:22</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>21 ex</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4828,32 +4828,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132432298</v>
+        <v>132432292</v>
       </c>
       <c r="B41" t="n">
-        <v>93180</v>
+        <v>79317</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4863,13 +4863,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>596089</v>
+        <v>596182</v>
       </c>
       <c r="R41" t="n">
-        <v>6966904</v>
+        <v>6966811</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4935,32 +4935,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132432292</v>
+        <v>132432298</v>
       </c>
       <c r="B42" t="n">
-        <v>79317</v>
+        <v>93180</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4970,13 +4970,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>596182</v>
+        <v>596089</v>
       </c>
       <c r="R42" t="n">
-        <v>6966811</v>
+        <v>6966904</v>
       </c>
       <c r="S42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5015,7 +5015,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 16147-2022 artfynd.xlsx
+++ b/artfynd/A 16147-2022 artfynd.xlsx
@@ -2438,7 +2438,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132432301</v>
+        <v>132432283</v>
       </c>
       <c r="B19" t="n">
         <v>79317</v>
@@ -2473,13 +2473,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596009</v>
+        <v>596032</v>
       </c>
       <c r="R19" t="n">
-        <v>6966905</v>
+        <v>6966998</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2545,7 +2545,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132432283</v>
+        <v>132432297</v>
       </c>
       <c r="B20" t="n">
         <v>79317</v>
@@ -2580,13 +2580,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596032</v>
+        <v>596078</v>
       </c>
       <c r="R20" t="n">
-        <v>6966998</v>
+        <v>6966887</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2652,7 +2652,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132432297</v>
+        <v>132432301</v>
       </c>
       <c r="B21" t="n">
         <v>79317</v>
@@ -2687,13 +2687,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596078</v>
+        <v>596009</v>
       </c>
       <c r="R21" t="n">
-        <v>6966887</v>
+        <v>6966905</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3842,7 +3842,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132432291</v>
+        <v>132432290</v>
       </c>
       <c r="B32" t="n">
         <v>79317</v>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>596166</v>
+        <v>596147</v>
       </c>
       <c r="R32" t="n">
-        <v>6966844</v>
+        <v>6966886</v>
       </c>
       <c r="S32" t="n">
         <v>6</v>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3949,7 +3949,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132432290</v>
+        <v>132432291</v>
       </c>
       <c r="B33" t="n">
         <v>79317</v>
@@ -3984,10 +3984,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>596147</v>
+        <v>596166</v>
       </c>
       <c r="R33" t="n">
-        <v>6966886</v>
+        <v>6966844</v>
       </c>
       <c r="S33" t="n">
         <v>6</v>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4828,32 +4828,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132432292</v>
+        <v>132432298</v>
       </c>
       <c r="B41" t="n">
-        <v>79317</v>
+        <v>93180</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4863,13 +4863,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>596182</v>
+        <v>596089</v>
       </c>
       <c r="R41" t="n">
-        <v>6966811</v>
+        <v>6966904</v>
       </c>
       <c r="S41" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4935,32 +4935,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132432298</v>
+        <v>132432292</v>
       </c>
       <c r="B42" t="n">
-        <v>93180</v>
+        <v>79317</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4970,13 +4970,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>596089</v>
+        <v>596182</v>
       </c>
       <c r="R42" t="n">
-        <v>6966904</v>
+        <v>6966811</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5015,7 +5015,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 16147-2022 artfynd.xlsx
+++ b/artfynd/A 16147-2022 artfynd.xlsx
@@ -1893,7 +1893,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132432280</v>
+        <v>132432279</v>
       </c>
       <c r="B14" t="n">
         <v>93180</v>
@@ -1928,13 +1928,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596064</v>
+        <v>596068</v>
       </c>
       <c r="R14" t="n">
-        <v>6966954</v>
+        <v>6966939</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1973,12 +1973,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>5 ex från förra året</t>
+          <t>14 fruktkroppar från förra året</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2005,7 +2005,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132432279</v>
+        <v>132432280</v>
       </c>
       <c r="B15" t="n">
         <v>93180</v>
@@ -2040,13 +2040,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596068</v>
+        <v>596064</v>
       </c>
       <c r="R15" t="n">
-        <v>6966939</v>
+        <v>6966954</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2085,12 +2085,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>14 fruktkroppar från förra året</t>
+          <t>5 ex från förra året</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2224,7 +2224,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132432286</v>
+        <v>132432274</v>
       </c>
       <c r="B17" t="n">
         <v>79317</v>
@@ -2259,13 +2259,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596083</v>
+        <v>596061</v>
       </c>
       <c r="R17" t="n">
-        <v>6966954</v>
+        <v>6967031</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2331,7 +2331,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132432274</v>
+        <v>132432286</v>
       </c>
       <c r="B18" t="n">
         <v>79317</v>
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596061</v>
+        <v>596083</v>
       </c>
       <c r="R18" t="n">
-        <v>6967031</v>
+        <v>6966954</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2438,7 +2438,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132432283</v>
+        <v>132432297</v>
       </c>
       <c r="B19" t="n">
         <v>79317</v>
@@ -2473,13 +2473,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596032</v>
+        <v>596078</v>
       </c>
       <c r="R19" t="n">
-        <v>6966998</v>
+        <v>6966887</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2545,7 +2545,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132432297</v>
+        <v>132432283</v>
       </c>
       <c r="B20" t="n">
         <v>79317</v>
@@ -2580,13 +2580,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596078</v>
+        <v>596032</v>
       </c>
       <c r="R20" t="n">
-        <v>6966887</v>
+        <v>6966998</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3842,7 +3842,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132432290</v>
+        <v>132432291</v>
       </c>
       <c r="B32" t="n">
         <v>79317</v>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>596147</v>
+        <v>596166</v>
       </c>
       <c r="R32" t="n">
-        <v>6966886</v>
+        <v>6966844</v>
       </c>
       <c r="S32" t="n">
         <v>6</v>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3949,7 +3949,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132432291</v>
+        <v>132432290</v>
       </c>
       <c r="B33" t="n">
         <v>79317</v>
@@ -3984,10 +3984,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>596166</v>
+        <v>596147</v>
       </c>
       <c r="R33" t="n">
-        <v>6966844</v>
+        <v>6966886</v>
       </c>
       <c r="S33" t="n">
         <v>6</v>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4387,32 +4387,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132432300</v>
+        <v>132432304</v>
       </c>
       <c r="B37" t="n">
-        <v>93180</v>
+        <v>79317</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4422,13 +4422,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>596083</v>
+        <v>596049</v>
       </c>
       <c r="R37" t="n">
-        <v>6966915</v>
+        <v>6966812</v>
       </c>
       <c r="S37" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4494,32 +4494,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132432304</v>
+        <v>132432300</v>
       </c>
       <c r="B38" t="n">
-        <v>79317</v>
+        <v>93180</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4529,13 +4529,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>596049</v>
+        <v>596083</v>
       </c>
       <c r="R38" t="n">
-        <v>6966812</v>
+        <v>6966915</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 16147-2022 artfynd.xlsx
+++ b/artfynd/A 16147-2022 artfynd.xlsx
@@ -4387,32 +4387,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132432304</v>
+        <v>132432300</v>
       </c>
       <c r="B37" t="n">
-        <v>79317</v>
+        <v>93180</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4422,13 +4422,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>596049</v>
+        <v>596083</v>
       </c>
       <c r="R37" t="n">
-        <v>6966812</v>
+        <v>6966915</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4494,32 +4494,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132432300</v>
+        <v>132432304</v>
       </c>
       <c r="B38" t="n">
-        <v>93180</v>
+        <v>79317</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4529,13 +4529,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>596083</v>
+        <v>596049</v>
       </c>
       <c r="R38" t="n">
-        <v>6966915</v>
+        <v>6966812</v>
       </c>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 16147-2022 artfynd.xlsx
+++ b/artfynd/A 16147-2022 artfynd.xlsx
@@ -4387,32 +4387,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132432300</v>
+        <v>132432304</v>
       </c>
       <c r="B37" t="n">
-        <v>93180</v>
+        <v>79317</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4422,13 +4422,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>596083</v>
+        <v>596049</v>
       </c>
       <c r="R37" t="n">
-        <v>6966915</v>
+        <v>6966812</v>
       </c>
       <c r="S37" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4494,32 +4494,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132432304</v>
+        <v>132432300</v>
       </c>
       <c r="B38" t="n">
-        <v>79317</v>
+        <v>93180</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4529,13 +4529,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>596049</v>
+        <v>596083</v>
       </c>
       <c r="R38" t="n">
-        <v>6966812</v>
+        <v>6966915</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 16147-2022 artfynd.xlsx
+++ b/artfynd/A 16147-2022 artfynd.xlsx
@@ -3414,32 +3414,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132432293</v>
+        <v>132432302</v>
       </c>
       <c r="B28" t="n">
-        <v>97963</v>
+        <v>79317</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3449,13 +3449,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>596185</v>
+        <v>595964</v>
       </c>
       <c r="R28" t="n">
-        <v>6966797</v>
+        <v>6966881</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3521,32 +3521,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132432302</v>
+        <v>132432293</v>
       </c>
       <c r="B29" t="n">
-        <v>79317</v>
+        <v>97963</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3556,13 +3556,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>595964</v>
+        <v>596185</v>
       </c>
       <c r="R29" t="n">
-        <v>6966881</v>
+        <v>6966797</v>
       </c>
       <c r="S29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 16147-2022 artfynd.xlsx
+++ b/artfynd/A 16147-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132081985</v>
       </c>
       <c r="B2" t="n">
-        <v>57127</v>
+        <v>57128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>132082483</v>
       </c>
       <c r="B3" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>132082058</v>
       </c>
       <c r="B4" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>132080892</v>
       </c>
       <c r="B5" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>132082444</v>
       </c>
       <c r="B6" t="n">
-        <v>83163</v>
+        <v>83165</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>132081105</v>
       </c>
       <c r="B7" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>132081052</v>
       </c>
       <c r="B8" t="n">
-        <v>92191</v>
+        <v>92197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>132081586</v>
       </c>
       <c r="B9" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>132081046</v>
       </c>
       <c r="B10" t="n">
-        <v>58109</v>
+        <v>58110</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>132432303</v>
       </c>
       <c r="B11" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>132432289</v>
       </c>
       <c r="B12" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>132432277</v>
       </c>
       <c r="B13" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1893,10 +1893,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132432279</v>
+        <v>132432280</v>
       </c>
       <c r="B14" t="n">
-        <v>93180</v>
+        <v>93186</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1928,13 +1928,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596068</v>
+        <v>596064</v>
       </c>
       <c r="R14" t="n">
-        <v>6966939</v>
+        <v>6966954</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1973,12 +1973,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>14 fruktkroppar från förra året</t>
+          <t>5 ex från förra året</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2005,10 +2005,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132432280</v>
+        <v>132432279</v>
       </c>
       <c r="B15" t="n">
-        <v>93180</v>
+        <v>93186</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2040,13 +2040,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596064</v>
+        <v>596068</v>
       </c>
       <c r="R15" t="n">
-        <v>6966954</v>
+        <v>6966939</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2085,12 +2085,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>5 ex från förra året</t>
+          <t>14 fruktkroppar från förra året</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2120,7 +2120,7 @@
         <v>132432294</v>
       </c>
       <c r="B16" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>132432274</v>
       </c>
       <c r="B17" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>132432286</v>
       </c>
       <c r="B18" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         <v>132432297</v>
       </c>
       <c r="B19" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2545,10 +2545,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132432283</v>
+        <v>132432301</v>
       </c>
       <c r="B20" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2580,13 +2580,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596032</v>
+        <v>596009</v>
       </c>
       <c r="R20" t="n">
-        <v>6966998</v>
+        <v>6966905</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2652,10 +2652,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132432301</v>
+        <v>132432283</v>
       </c>
       <c r="B21" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2687,13 +2687,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596009</v>
+        <v>596032</v>
       </c>
       <c r="R21" t="n">
-        <v>6966905</v>
+        <v>6966998</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2762,7 +2762,7 @@
         <v>132432306</v>
       </c>
       <c r="B22" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>132432282</v>
       </c>
       <c r="B23" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>132432299</v>
       </c>
       <c r="B24" t="n">
-        <v>93180</v>
+        <v>93186</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>132432288</v>
       </c>
       <c r="B25" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>132432278</v>
       </c>
       <c r="B26" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>132432305</v>
       </c>
       <c r="B27" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>132432302</v>
       </c>
       <c r="B28" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>132432293</v>
       </c>
       <c r="B29" t="n">
-        <v>97963</v>
+        <v>97971</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3628,10 +3628,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132432275</v>
+        <v>132432281</v>
       </c>
       <c r="B30" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3663,13 +3663,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>596090</v>
+        <v>596063</v>
       </c>
       <c r="R30" t="n">
-        <v>6967008</v>
+        <v>6966956</v>
       </c>
       <c r="S30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3735,10 +3735,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132432281</v>
+        <v>132432275</v>
       </c>
       <c r="B31" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3770,13 +3770,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>596063</v>
+        <v>596090</v>
       </c>
       <c r="R31" t="n">
-        <v>6966956</v>
+        <v>6967008</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3842,10 +3842,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132432291</v>
+        <v>132432290</v>
       </c>
       <c r="B32" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>596166</v>
+        <v>596147</v>
       </c>
       <c r="R32" t="n">
-        <v>6966844</v>
+        <v>6966886</v>
       </c>
       <c r="S32" t="n">
         <v>6</v>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3949,10 +3949,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132432290</v>
+        <v>132432291</v>
       </c>
       <c r="B33" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3984,10 +3984,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>596147</v>
+        <v>596166</v>
       </c>
       <c r="R33" t="n">
-        <v>6966886</v>
+        <v>6966844</v>
       </c>
       <c r="S33" t="n">
         <v>6</v>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4059,7 +4059,7 @@
         <v>132432295</v>
       </c>
       <c r="B34" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>132432296</v>
       </c>
       <c r="B35" t="n">
-        <v>93180</v>
+        <v>93186</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4275,32 +4275,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132432285</v>
+        <v>132432300</v>
       </c>
       <c r="B36" t="n">
-        <v>99098</v>
+        <v>93186</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>596048</v>
+        <v>596083</v>
       </c>
       <c r="R36" t="n">
-        <v>6967002</v>
+        <v>6966915</v>
       </c>
       <c r="S36" t="n">
         <v>7</v>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4355,12 +4355,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:22</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>21 ex</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4390,7 +4385,7 @@
         <v>132432304</v>
       </c>
       <c r="B37" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4494,32 +4489,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132432300</v>
+        <v>132432285</v>
       </c>
       <c r="B38" t="n">
-        <v>93180</v>
+        <v>99106</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4529,10 +4524,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>596083</v>
+        <v>596048</v>
       </c>
       <c r="R38" t="n">
-        <v>6966915</v>
+        <v>6967002</v>
       </c>
       <c r="S38" t="n">
         <v>7</v>
@@ -4564,7 +4559,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4574,7 +4569,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>21 ex</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4601,10 +4601,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132432287</v>
+        <v>132432307</v>
       </c>
       <c r="B39" t="n">
-        <v>79317</v>
+        <v>57949</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4612,37 +4612,45 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Remmen, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>596092</v>
+        <v>596056</v>
       </c>
       <c r="R39" t="n">
-        <v>6966931</v>
+        <v>6966834</v>
       </c>
       <c r="S39" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4671,7 +4679,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4681,7 +4689,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4708,10 +4721,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132432307</v>
+        <v>132432287</v>
       </c>
       <c r="B40" t="n">
-        <v>57948</v>
+        <v>79319</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4719,45 +4732,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Remmen, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>596056</v>
+        <v>596092</v>
       </c>
       <c r="R40" t="n">
-        <v>6966834</v>
+        <v>6966931</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4786,7 +4791,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4796,12 +4801,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:33</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4831,7 +4831,7 @@
         <v>132432298</v>
       </c>
       <c r="B41" t="n">
-        <v>93180</v>
+        <v>93186</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>132432292</v>
       </c>
       <c r="B42" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 16147-2022 artfynd.xlsx
+++ b/artfynd/A 16147-2022 artfynd.xlsx
@@ -2117,7 +2117,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132432294</v>
+        <v>132432286</v>
       </c>
       <c r="B16" t="n">
         <v>79319</v>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596130</v>
+        <v>596083</v>
       </c>
       <c r="R16" t="n">
-        <v>6966823</v>
+        <v>6966954</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2224,7 +2224,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132432274</v>
+        <v>132432294</v>
       </c>
       <c r="B17" t="n">
         <v>79319</v>
@@ -2259,13 +2259,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596061</v>
+        <v>596130</v>
       </c>
       <c r="R17" t="n">
-        <v>6967031</v>
+        <v>6966823</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2331,7 +2331,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132432286</v>
+        <v>132432274</v>
       </c>
       <c r="B18" t="n">
         <v>79319</v>
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596083</v>
+        <v>596061</v>
       </c>
       <c r="R18" t="n">
-        <v>6966954</v>
+        <v>6967031</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2438,7 +2438,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132432297</v>
+        <v>132432283</v>
       </c>
       <c r="B19" t="n">
         <v>79319</v>
@@ -2473,13 +2473,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596078</v>
+        <v>596032</v>
       </c>
       <c r="R19" t="n">
-        <v>6966887</v>
+        <v>6966998</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2545,7 +2545,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132432301</v>
+        <v>132432297</v>
       </c>
       <c r="B20" t="n">
         <v>79319</v>
@@ -2580,13 +2580,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596009</v>
+        <v>596078</v>
       </c>
       <c r="R20" t="n">
-        <v>6966905</v>
+        <v>6966887</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2652,7 +2652,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132432283</v>
+        <v>132432301</v>
       </c>
       <c r="B21" t="n">
         <v>79319</v>
@@ -2687,13 +2687,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596032</v>
+        <v>596009</v>
       </c>
       <c r="R21" t="n">
-        <v>6966998</v>
+        <v>6966905</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -4275,32 +4275,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132432300</v>
+        <v>132432285</v>
       </c>
       <c r="B36" t="n">
-        <v>93186</v>
+        <v>99106</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>596083</v>
+        <v>596048</v>
       </c>
       <c r="R36" t="n">
-        <v>6966915</v>
+        <v>6967002</v>
       </c>
       <c r="S36" t="n">
         <v>7</v>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4355,7 +4355,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>21 ex</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4382,32 +4387,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132432304</v>
+        <v>132432300</v>
       </c>
       <c r="B37" t="n">
-        <v>79319</v>
+        <v>93186</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4417,13 +4422,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>596049</v>
+        <v>596083</v>
       </c>
       <c r="R37" t="n">
-        <v>6966812</v>
+        <v>6966915</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4452,7 +4457,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4462,7 +4467,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4489,32 +4494,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132432285</v>
+        <v>132432304</v>
       </c>
       <c r="B38" t="n">
-        <v>99106</v>
+        <v>79319</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4524,13 +4529,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>596048</v>
+        <v>596049</v>
       </c>
       <c r="R38" t="n">
-        <v>6967002</v>
+        <v>6966812</v>
       </c>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4559,7 +4564,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4569,12 +4574,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:22</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>21 ex</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 16147-2022 artfynd.xlsx
+++ b/artfynd/A 16147-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132081985</v>
       </c>
       <c r="B2" t="n">
-        <v>57128</v>
+        <v>57132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>132082483</v>
       </c>
       <c r="B3" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>132082058</v>
       </c>
       <c r="B4" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>132080892</v>
       </c>
       <c r="B5" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>132082444</v>
       </c>
       <c r="B6" t="n">
-        <v>83165</v>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>132081105</v>
       </c>
       <c r="B7" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>132081052</v>
       </c>
       <c r="B8" t="n">
-        <v>92197</v>
+        <v>92207</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>132081586</v>
       </c>
       <c r="B9" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>132081046</v>
       </c>
       <c r="B10" t="n">
-        <v>58110</v>
+        <v>58114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>132432303</v>
       </c>
       <c r="B11" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>132432289</v>
       </c>
       <c r="B12" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>132432277</v>
       </c>
       <c r="B13" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1893,10 +1893,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132432280</v>
+        <v>132432279</v>
       </c>
       <c r="B14" t="n">
-        <v>93186</v>
+        <v>93196</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1928,13 +1928,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596064</v>
+        <v>596068</v>
       </c>
       <c r="R14" t="n">
-        <v>6966954</v>
+        <v>6966939</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1973,12 +1973,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>5 ex från förra året</t>
+          <t>14 fruktkroppar från förra året</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2005,10 +2005,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132432279</v>
+        <v>132432280</v>
       </c>
       <c r="B15" t="n">
-        <v>93186</v>
+        <v>93196</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2040,13 +2040,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596068</v>
+        <v>596064</v>
       </c>
       <c r="R15" t="n">
-        <v>6966939</v>
+        <v>6966954</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2085,12 +2085,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>14 fruktkroppar från förra året</t>
+          <t>5 ex från förra året</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2117,10 +2117,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132432286</v>
+        <v>132432294</v>
       </c>
       <c r="B16" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596083</v>
+        <v>596130</v>
       </c>
       <c r="R16" t="n">
-        <v>6966954</v>
+        <v>6966823</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2224,10 +2224,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132432294</v>
+        <v>132432274</v>
       </c>
       <c r="B17" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,13 +2259,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596130</v>
+        <v>596061</v>
       </c>
       <c r="R17" t="n">
-        <v>6966823</v>
+        <v>6967031</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2331,10 +2331,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132432274</v>
+        <v>132432286</v>
       </c>
       <c r="B18" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596061</v>
+        <v>596083</v>
       </c>
       <c r="R18" t="n">
-        <v>6967031</v>
+        <v>6966954</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2438,10 +2438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132432283</v>
+        <v>132432297</v>
       </c>
       <c r="B19" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2473,13 +2473,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596032</v>
+        <v>596078</v>
       </c>
       <c r="R19" t="n">
-        <v>6966998</v>
+        <v>6966887</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2545,10 +2545,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132432297</v>
+        <v>132432283</v>
       </c>
       <c r="B20" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2580,13 +2580,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596078</v>
+        <v>596032</v>
       </c>
       <c r="R20" t="n">
-        <v>6966887</v>
+        <v>6966998</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2655,7 +2655,7 @@
         <v>132432301</v>
       </c>
       <c r="B21" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>132432306</v>
       </c>
       <c r="B22" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>132432282</v>
       </c>
       <c r="B23" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>132432299</v>
       </c>
       <c r="B24" t="n">
-        <v>93186</v>
+        <v>93196</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>132432288</v>
       </c>
       <c r="B25" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>132432278</v>
       </c>
       <c r="B26" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>132432305</v>
       </c>
       <c r="B27" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3414,32 +3414,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132432302</v>
+        <v>132432293</v>
       </c>
       <c r="B28" t="n">
-        <v>79319</v>
+        <v>97981</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3449,13 +3449,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>595964</v>
+        <v>596185</v>
       </c>
       <c r="R28" t="n">
-        <v>6966881</v>
+        <v>6966797</v>
       </c>
       <c r="S28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3521,32 +3521,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132432293</v>
+        <v>132432302</v>
       </c>
       <c r="B29" t="n">
-        <v>97971</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3556,13 +3556,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>596185</v>
+        <v>595964</v>
       </c>
       <c r="R29" t="n">
-        <v>6966797</v>
+        <v>6966881</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3628,10 +3628,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132432281</v>
+        <v>132432275</v>
       </c>
       <c r="B30" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3663,13 +3663,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>596063</v>
+        <v>596090</v>
       </c>
       <c r="R30" t="n">
-        <v>6966956</v>
+        <v>6967008</v>
       </c>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3735,10 +3735,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132432275</v>
+        <v>132432281</v>
       </c>
       <c r="B31" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3770,13 +3770,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>596090</v>
+        <v>596063</v>
       </c>
       <c r="R31" t="n">
-        <v>6967008</v>
+        <v>6966956</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3842,10 +3842,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132432290</v>
+        <v>132432291</v>
       </c>
       <c r="B32" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>596147</v>
+        <v>596166</v>
       </c>
       <c r="R32" t="n">
-        <v>6966886</v>
+        <v>6966844</v>
       </c>
       <c r="S32" t="n">
         <v>6</v>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3949,10 +3949,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132432291</v>
+        <v>132432290</v>
       </c>
       <c r="B33" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3984,10 +3984,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>596166</v>
+        <v>596147</v>
       </c>
       <c r="R33" t="n">
-        <v>6966844</v>
+        <v>6966886</v>
       </c>
       <c r="S33" t="n">
         <v>6</v>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4059,7 +4059,7 @@
         <v>132432295</v>
       </c>
       <c r="B34" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>132432296</v>
       </c>
       <c r="B35" t="n">
-        <v>93186</v>
+        <v>93196</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4275,32 +4275,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132432285</v>
+        <v>132432304</v>
       </c>
       <c r="B36" t="n">
-        <v>99106</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4310,13 +4310,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>596048</v>
+        <v>596049</v>
       </c>
       <c r="R36" t="n">
-        <v>6967002</v>
+        <v>6966812</v>
       </c>
       <c r="S36" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4355,12 +4355,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:22</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>21 ex</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4390,7 +4385,7 @@
         <v>132432300</v>
       </c>
       <c r="B37" t="n">
-        <v>93186</v>
+        <v>93196</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4494,32 +4489,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132432304</v>
+        <v>132432285</v>
       </c>
       <c r="B38" t="n">
-        <v>79319</v>
+        <v>99116</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4529,13 +4524,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>596049</v>
+        <v>596048</v>
       </c>
       <c r="R38" t="n">
-        <v>6966812</v>
+        <v>6967002</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4564,7 +4559,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4574,7 +4569,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>21 ex</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4604,7 +4604,7 @@
         <v>132432307</v>
       </c>
       <c r="B39" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>132432287</v>
       </c>
       <c r="B40" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>132432298</v>
       </c>
       <c r="B41" t="n">
-        <v>93186</v>
+        <v>93196</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>132432292</v>
       </c>
       <c r="B42" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 16147-2022 artfynd.xlsx
+++ b/artfynd/A 16147-2022 artfynd.xlsx
@@ -1896,7 +1896,7 @@
         <v>132432279</v>
       </c>
       <c r="B14" t="n">
-        <v>93196</v>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>132432280</v>
       </c>
       <c r="B15" t="n">
-        <v>93196</v>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>132432299</v>
       </c>
       <c r="B24" t="n">
-        <v>93196</v>
+        <v>93197</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3414,32 +3414,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132432293</v>
+        <v>132432302</v>
       </c>
       <c r="B28" t="n">
-        <v>97981</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3449,13 +3449,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>596185</v>
+        <v>595964</v>
       </c>
       <c r="R28" t="n">
-        <v>6966797</v>
+        <v>6966881</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3521,32 +3521,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132432302</v>
+        <v>132432293</v>
       </c>
       <c r="B29" t="n">
-        <v>79327</v>
+        <v>97982</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3556,13 +3556,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>595964</v>
+        <v>596185</v>
       </c>
       <c r="R29" t="n">
-        <v>6966881</v>
+        <v>6966797</v>
       </c>
       <c r="S29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4166,7 +4166,7 @@
         <v>132432296</v>
       </c>
       <c r="B35" t="n">
-        <v>93196</v>
+        <v>93197</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>132432300</v>
       </c>
       <c r="B37" t="n">
-        <v>93196</v>
+        <v>93197</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>132432285</v>
       </c>
       <c r="B38" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4601,10 +4601,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132432307</v>
+        <v>132432287</v>
       </c>
       <c r="B39" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4612,45 +4612,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Remmen, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>596056</v>
+        <v>596092</v>
       </c>
       <c r="R39" t="n">
-        <v>6966834</v>
+        <v>6966931</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4679,7 +4671,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4689,12 +4681,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:33</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4721,10 +4708,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132432287</v>
+        <v>132432307</v>
       </c>
       <c r="B40" t="n">
-        <v>79327</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4732,37 +4719,45 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Remmen, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>596092</v>
+        <v>596056</v>
       </c>
       <c r="R40" t="n">
-        <v>6966931</v>
+        <v>6966834</v>
       </c>
       <c r="S40" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4791,7 +4786,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4801,7 +4796,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4831,7 +4831,7 @@
         <v>132432298</v>
       </c>
       <c r="B41" t="n">
-        <v>93196</v>
+        <v>93197</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 16147-2022 artfynd.xlsx
+++ b/artfynd/A 16147-2022 artfynd.xlsx
@@ -1178,7 +1178,7 @@
         <v>132081105</v>
       </c>
       <c r="B7" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>132081052</v>
       </c>
       <c r="B8" t="n">
-        <v>92207</v>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132432279</v>
+        <v>132432280</v>
       </c>
       <c r="B14" t="n">
         <v>93197</v>
@@ -1928,13 +1928,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596068</v>
+        <v>596064</v>
       </c>
       <c r="R14" t="n">
-        <v>6966939</v>
+        <v>6966954</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1973,12 +1973,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>14 fruktkroppar från förra året</t>
+          <t>5 ex från förra året</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2005,7 +2005,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132432280</v>
+        <v>132432279</v>
       </c>
       <c r="B15" t="n">
         <v>93197</v>
@@ -2040,13 +2040,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596064</v>
+        <v>596068</v>
       </c>
       <c r="R15" t="n">
-        <v>6966954</v>
+        <v>6966939</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2085,12 +2085,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>5 ex från förra året</t>
+          <t>14 fruktkroppar från förra året</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -3414,32 +3414,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132432302</v>
+        <v>132432293</v>
       </c>
       <c r="B28" t="n">
-        <v>79327</v>
+        <v>97983</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3449,13 +3449,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>595964</v>
+        <v>596185</v>
       </c>
       <c r="R28" t="n">
-        <v>6966881</v>
+        <v>6966797</v>
       </c>
       <c r="S28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3521,32 +3521,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132432293</v>
+        <v>132432302</v>
       </c>
       <c r="B29" t="n">
-        <v>97982</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3556,13 +3556,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>596185</v>
+        <v>595964</v>
       </c>
       <c r="R29" t="n">
-        <v>6966797</v>
+        <v>6966881</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4275,32 +4275,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132432304</v>
+        <v>132432285</v>
       </c>
       <c r="B36" t="n">
-        <v>79327</v>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4310,13 +4310,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>596049</v>
+        <v>596048</v>
       </c>
       <c r="R36" t="n">
-        <v>6966812</v>
+        <v>6967002</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4355,7 +4355,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>21 ex</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4489,32 +4494,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132432285</v>
+        <v>132432304</v>
       </c>
       <c r="B38" t="n">
-        <v>99117</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4524,13 +4529,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>596048</v>
+        <v>596049</v>
       </c>
       <c r="R38" t="n">
-        <v>6967002</v>
+        <v>6966812</v>
       </c>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4559,7 +4564,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4569,12 +4574,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:22</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>21 ex</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4601,10 +4601,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132432287</v>
+        <v>132432307</v>
       </c>
       <c r="B39" t="n">
-        <v>79327</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4612,37 +4612,45 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Remmen, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>596092</v>
+        <v>596056</v>
       </c>
       <c r="R39" t="n">
-        <v>6966931</v>
+        <v>6966834</v>
       </c>
       <c r="S39" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4671,7 +4679,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4681,7 +4689,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4708,10 +4721,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132432307</v>
+        <v>132432287</v>
       </c>
       <c r="B40" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4719,45 +4732,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Remmen, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>596056</v>
+        <v>596092</v>
       </c>
       <c r="R40" t="n">
-        <v>6966834</v>
+        <v>6966931</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4786,7 +4791,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4796,12 +4801,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:33</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 16147-2022 artfynd.xlsx
+++ b/artfynd/A 16147-2022 artfynd.xlsx
@@ -3414,32 +3414,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132432293</v>
+        <v>132432302</v>
       </c>
       <c r="B28" t="n">
-        <v>97983</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3449,13 +3449,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>596185</v>
+        <v>595964</v>
       </c>
       <c r="R28" t="n">
-        <v>6966797</v>
+        <v>6966881</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3521,32 +3521,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132432302</v>
+        <v>132432293</v>
       </c>
       <c r="B29" t="n">
-        <v>79327</v>
+        <v>97983</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3556,13 +3556,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>595964</v>
+        <v>596185</v>
       </c>
       <c r="R29" t="n">
-        <v>6966881</v>
+        <v>6966797</v>
       </c>
       <c r="S29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4275,32 +4275,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132432285</v>
+        <v>132432304</v>
       </c>
       <c r="B36" t="n">
-        <v>99118</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4310,13 +4310,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>596048</v>
+        <v>596049</v>
       </c>
       <c r="R36" t="n">
-        <v>6967002</v>
+        <v>6966812</v>
       </c>
       <c r="S36" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4355,12 +4355,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:22</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>21 ex</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4494,32 +4489,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132432304</v>
+        <v>132432285</v>
       </c>
       <c r="B38" t="n">
-        <v>79327</v>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4529,13 +4524,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>596049</v>
+        <v>596048</v>
       </c>
       <c r="R38" t="n">
-        <v>6966812</v>
+        <v>6967002</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4564,7 +4559,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4574,7 +4569,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>21 ex</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4601,10 +4601,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132432307</v>
+        <v>132432287</v>
       </c>
       <c r="B39" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4612,45 +4612,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Remmen, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>596056</v>
+        <v>596092</v>
       </c>
       <c r="R39" t="n">
-        <v>6966834</v>
+        <v>6966931</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4679,7 +4671,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4689,12 +4681,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:33</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4721,10 +4708,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132432287</v>
+        <v>132432307</v>
       </c>
       <c r="B40" t="n">
-        <v>79327</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4732,37 +4719,45 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Remmen, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>596092</v>
+        <v>596056</v>
       </c>
       <c r="R40" t="n">
-        <v>6966931</v>
+        <v>6966834</v>
       </c>
       <c r="S40" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4791,7 +4786,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4801,7 +4796,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 16147-2022 artfynd.xlsx
+++ b/artfynd/A 16147-2022 artfynd.xlsx
@@ -1893,7 +1893,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132432280</v>
+        <v>132432279</v>
       </c>
       <c r="B14" t="n">
         <v>93197</v>
@@ -1928,13 +1928,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596064</v>
+        <v>596068</v>
       </c>
       <c r="R14" t="n">
-        <v>6966954</v>
+        <v>6966939</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1973,12 +1973,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>5 ex från förra året</t>
+          <t>14 fruktkroppar från förra året</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2005,7 +2005,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132432279</v>
+        <v>132432280</v>
       </c>
       <c r="B15" t="n">
         <v>93197</v>
@@ -2040,13 +2040,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596068</v>
+        <v>596064</v>
       </c>
       <c r="R15" t="n">
-        <v>6966939</v>
+        <v>6966954</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2085,12 +2085,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>14 fruktkroppar från förra året</t>
+          <t>5 ex från förra året</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -4275,32 +4275,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132432304</v>
+        <v>132432300</v>
       </c>
       <c r="B36" t="n">
-        <v>79327</v>
+        <v>93197</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4310,13 +4310,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>596049</v>
+        <v>596083</v>
       </c>
       <c r="R36" t="n">
-        <v>6966812</v>
+        <v>6966915</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4382,32 +4382,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132432300</v>
+        <v>132432285</v>
       </c>
       <c r="B37" t="n">
-        <v>93197</v>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4417,10 +4417,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>596083</v>
+        <v>596048</v>
       </c>
       <c r="R37" t="n">
-        <v>6966915</v>
+        <v>6967002</v>
       </c>
       <c r="S37" t="n">
         <v>7</v>
@@ -4452,7 +4452,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4462,7 +4462,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>21 ex</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4489,32 +4494,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132432285</v>
+        <v>132432304</v>
       </c>
       <c r="B38" t="n">
-        <v>99118</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4524,13 +4529,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>596048</v>
+        <v>596049</v>
       </c>
       <c r="R38" t="n">
-        <v>6967002</v>
+        <v>6966812</v>
       </c>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4559,7 +4564,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4569,12 +4574,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:22</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>21 ex</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4828,32 +4828,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132432298</v>
+        <v>132432292</v>
       </c>
       <c r="B41" t="n">
-        <v>93197</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4863,13 +4863,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>596089</v>
+        <v>596182</v>
       </c>
       <c r="R41" t="n">
-        <v>6966904</v>
+        <v>6966811</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4935,32 +4935,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132432292</v>
+        <v>132432298</v>
       </c>
       <c r="B42" t="n">
-        <v>79327</v>
+        <v>93197</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4970,13 +4970,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>596182</v>
+        <v>596089</v>
       </c>
       <c r="R42" t="n">
-        <v>6966811</v>
+        <v>6966904</v>
       </c>
       <c r="S42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5015,7 +5015,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 16147-2022 artfynd.xlsx
+++ b/artfynd/A 16147-2022 artfynd.xlsx
@@ -3414,32 +3414,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132432302</v>
+        <v>132432293</v>
       </c>
       <c r="B28" t="n">
-        <v>79327</v>
+        <v>97983</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3449,13 +3449,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>595964</v>
+        <v>596185</v>
       </c>
       <c r="R28" t="n">
-        <v>6966881</v>
+        <v>6966797</v>
       </c>
       <c r="S28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3521,32 +3521,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132432293</v>
+        <v>132432302</v>
       </c>
       <c r="B29" t="n">
-        <v>97983</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3556,13 +3556,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>596185</v>
+        <v>595964</v>
       </c>
       <c r="R29" t="n">
-        <v>6966797</v>
+        <v>6966881</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 16147-2022 artfynd.xlsx
+++ b/artfynd/A 16147-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132081985</v>
       </c>
       <c r="B2" t="n">
-        <v>57132</v>
+        <v>57133</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>132082483</v>
       </c>
       <c r="B3" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>132082058</v>
       </c>
       <c r="B4" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>132080892</v>
       </c>
       <c r="B5" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>132082444</v>
       </c>
       <c r="B6" t="n">
-        <v>83173</v>
+        <v>83174</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>132081105</v>
       </c>
       <c r="B7" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>132081052</v>
       </c>
       <c r="B8" t="n">
-        <v>92208</v>
+        <v>92209</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>132081586</v>
       </c>
       <c r="B9" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>132081046</v>
       </c>
       <c r="B10" t="n">
-        <v>58114</v>
+        <v>58115</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>132432303</v>
       </c>
       <c r="B11" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>132432289</v>
       </c>
       <c r="B12" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>132432277</v>
       </c>
       <c r="B13" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1893,10 +1893,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132432279</v>
+        <v>132432280</v>
       </c>
       <c r="B14" t="n">
-        <v>93197</v>
+        <v>93198</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1928,13 +1928,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596068</v>
+        <v>596064</v>
       </c>
       <c r="R14" t="n">
-        <v>6966939</v>
+        <v>6966954</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1973,12 +1973,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>14 fruktkroppar från förra året</t>
+          <t>5 ex från förra året</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2005,10 +2005,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132432280</v>
+        <v>132432279</v>
       </c>
       <c r="B15" t="n">
-        <v>93197</v>
+        <v>93198</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2040,13 +2040,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596064</v>
+        <v>596068</v>
       </c>
       <c r="R15" t="n">
-        <v>6966954</v>
+        <v>6966939</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2085,12 +2085,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>5 ex från förra året</t>
+          <t>14 fruktkroppar från förra året</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2117,10 +2117,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132432294</v>
+        <v>132432286</v>
       </c>
       <c r="B16" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596130</v>
+        <v>596083</v>
       </c>
       <c r="R16" t="n">
-        <v>6966823</v>
+        <v>6966954</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2227,7 +2227,7 @@
         <v>132432274</v>
       </c>
       <c r="B17" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2331,10 +2331,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132432286</v>
+        <v>132432294</v>
       </c>
       <c r="B18" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596083</v>
+        <v>596130</v>
       </c>
       <c r="R18" t="n">
-        <v>6966954</v>
+        <v>6966823</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2438,10 +2438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132432297</v>
+        <v>132432301</v>
       </c>
       <c r="B19" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2473,13 +2473,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596078</v>
+        <v>596009</v>
       </c>
       <c r="R19" t="n">
-        <v>6966887</v>
+        <v>6966905</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2548,7 +2548,7 @@
         <v>132432283</v>
       </c>
       <c r="B20" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2652,10 +2652,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132432301</v>
+        <v>132432297</v>
       </c>
       <c r="B21" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2687,13 +2687,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596009</v>
+        <v>596078</v>
       </c>
       <c r="R21" t="n">
-        <v>6966905</v>
+        <v>6966887</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2762,7 +2762,7 @@
         <v>132432306</v>
       </c>
       <c r="B22" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>132432282</v>
       </c>
       <c r="B23" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>132432299</v>
       </c>
       <c r="B24" t="n">
-        <v>93197</v>
+        <v>93198</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>132432288</v>
       </c>
       <c r="B25" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>132432278</v>
       </c>
       <c r="B26" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>132432305</v>
       </c>
       <c r="B27" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3414,32 +3414,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132432293</v>
+        <v>132432302</v>
       </c>
       <c r="B28" t="n">
-        <v>97983</v>
+        <v>79328</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3449,13 +3449,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>596185</v>
+        <v>595964</v>
       </c>
       <c r="R28" t="n">
-        <v>6966797</v>
+        <v>6966881</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3521,32 +3521,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132432302</v>
+        <v>132432293</v>
       </c>
       <c r="B29" t="n">
-        <v>79327</v>
+        <v>97984</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3556,13 +3556,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>595964</v>
+        <v>596185</v>
       </c>
       <c r="R29" t="n">
-        <v>6966881</v>
+        <v>6966797</v>
       </c>
       <c r="S29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3631,7 +3631,7 @@
         <v>132432275</v>
       </c>
       <c r="B30" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>132432281</v>
       </c>
       <c r="B31" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3842,10 +3842,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132432291</v>
+        <v>132432290</v>
       </c>
       <c r="B32" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>596166</v>
+        <v>596147</v>
       </c>
       <c r="R32" t="n">
-        <v>6966844</v>
+        <v>6966886</v>
       </c>
       <c r="S32" t="n">
         <v>6</v>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3949,10 +3949,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132432290</v>
+        <v>132432291</v>
       </c>
       <c r="B33" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3984,10 +3984,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>596147</v>
+        <v>596166</v>
       </c>
       <c r="R33" t="n">
-        <v>6966886</v>
+        <v>6966844</v>
       </c>
       <c r="S33" t="n">
         <v>6</v>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4059,7 +4059,7 @@
         <v>132432295</v>
       </c>
       <c r="B34" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>132432296</v>
       </c>
       <c r="B35" t="n">
-        <v>93197</v>
+        <v>93198</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4275,32 +4275,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132432300</v>
+        <v>132432285</v>
       </c>
       <c r="B36" t="n">
-        <v>93197</v>
+        <v>99119</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>596083</v>
+        <v>596048</v>
       </c>
       <c r="R36" t="n">
-        <v>6966915</v>
+        <v>6967002</v>
       </c>
       <c r="S36" t="n">
         <v>7</v>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4355,7 +4355,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>21 ex</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4382,32 +4387,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132432285</v>
+        <v>132432300</v>
       </c>
       <c r="B37" t="n">
-        <v>99118</v>
+        <v>93198</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4417,10 +4422,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>596048</v>
+        <v>596083</v>
       </c>
       <c r="R37" t="n">
-        <v>6967002</v>
+        <v>6966915</v>
       </c>
       <c r="S37" t="n">
         <v>7</v>
@@ -4452,7 +4457,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4462,12 +4467,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:22</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>21 ex</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4497,7 +4497,7 @@
         <v>132432304</v>
       </c>
       <c r="B38" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>132432287</v>
       </c>
       <c r="B39" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>132432307</v>
       </c>
       <c r="B40" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4828,32 +4828,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132432292</v>
+        <v>132432298</v>
       </c>
       <c r="B41" t="n">
-        <v>79327</v>
+        <v>93198</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4863,13 +4863,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>596182</v>
+        <v>596089</v>
       </c>
       <c r="R41" t="n">
-        <v>6966811</v>
+        <v>6966904</v>
       </c>
       <c r="S41" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4935,32 +4935,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132432298</v>
+        <v>132432292</v>
       </c>
       <c r="B42" t="n">
-        <v>93197</v>
+        <v>79328</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4970,13 +4970,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>596089</v>
+        <v>596182</v>
       </c>
       <c r="R42" t="n">
-        <v>6966904</v>
+        <v>6966811</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5015,7 +5015,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
